--- a/서류리스트.xlsx
+++ b/서류리스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\smart-logstics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD063710-9C8A-4CB2-A801-459359A4FF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFFCB62E-40E6-430B-A943-4AF5F94C43EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15420" yWindow="16080" windowWidth="29040" windowHeight="17520" xr2:uid="{C722C9AC-CAB8-40C6-8CCB-1BE659AFD812}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>필요서류 리스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -184,6 +184,10 @@
   </si>
   <si>
     <t>작성중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260721 공유(정유림님)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -984,28 +988,30 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="7">
         <v>16</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="9">
         <v>46213</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="8" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
